--- a/config/yunying/banner.xlsx
+++ b/config/yunying/banner.xlsx
@@ -314,7 +314,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,18 +324,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -352,13 +341,19 @@
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -849,137 +844,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -992,52 +987,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1361,9 +1332,9 @@
     <col min="5" max="5" width="45.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="31.125" style="1" customWidth="1"/>
     <col min="7" max="8" width="17.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.75" style="3" customWidth="1"/>
-    <col min="10" max="10" width="17.875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.75" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.75" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1389,16 +1360,16 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1424,16 +1395,16 @@
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="H2" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I2" s="3">
         <v>100</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="3">
         <v>20301230</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="3">
         <v>100</v>
       </c>
     </row>
@@ -1459,16 +1430,16 @@
       <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1485,19 +1456,19 @@
       <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I4" s="5">
-        <v>500</v>
-      </c>
-      <c r="J4" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K4" s="5">
+      <c r="H4" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I4" s="3">
+        <v>500</v>
+      </c>
+      <c r="J4" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K4" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1514,19 +1485,19 @@
       <c r="D5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I5" s="5">
-        <v>500</v>
-      </c>
-      <c r="J5" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K5" s="5">
+      <c r="H5" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I5" s="3">
+        <v>500</v>
+      </c>
+      <c r="J5" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K5" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1543,19 +1514,19 @@
       <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I6" s="5">
-        <v>500</v>
-      </c>
-      <c r="J6" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K6" s="5">
+      <c r="H6" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I6" s="3">
+        <v>500</v>
+      </c>
+      <c r="J6" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K6" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1572,19 +1543,19 @@
       <c r="D7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I7" s="5">
-        <v>500</v>
-      </c>
-      <c r="J7" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K7" s="5">
+      <c r="H7" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I7" s="3">
+        <v>500</v>
+      </c>
+      <c r="J7" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K7" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1601,19 +1572,19 @@
       <c r="D8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I8" s="5">
-        <v>500</v>
-      </c>
-      <c r="J8" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K8" s="5">
+      <c r="H8" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I8" s="3">
+        <v>500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K8" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1630,19 +1601,19 @@
       <c r="D9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I9" s="5">
-        <v>500</v>
-      </c>
-      <c r="J9" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K9" s="5">
+      <c r="H9" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I9" s="3">
+        <v>500</v>
+      </c>
+      <c r="J9" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K9" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1659,19 +1630,19 @@
       <c r="D10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I10" s="5">
-        <v>500</v>
-      </c>
-      <c r="J10" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K10" s="5">
+      <c r="H10" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I10" s="3">
+        <v>500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K10" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1688,28 +1659,28 @@
       <c r="D11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I11" s="5">
-        <v>500</v>
-      </c>
-      <c r="J11" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K11" s="5">
+      <c r="H11" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I11" s="3">
+        <v>500</v>
+      </c>
+      <c r="J11" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K11" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:11">
-      <c r="F12" s="6"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="5"/>
+      <c r="F12" s="4"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="3"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:11">
       <c r="A13" s="1">
@@ -1724,19 +1695,19 @@
       <c r="D13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I13" s="5">
-        <v>500</v>
-      </c>
-      <c r="J13" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K13" s="5">
+      <c r="H13" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I13" s="3">
+        <v>500</v>
+      </c>
+      <c r="J13" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K13" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1753,19 +1724,19 @@
       <c r="D14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I14" s="5">
-        <v>500</v>
-      </c>
-      <c r="J14" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K14" s="5">
+      <c r="H14" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I14" s="3">
+        <v>500</v>
+      </c>
+      <c r="J14" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K14" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1782,19 +1753,19 @@
       <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I15" s="5">
-        <v>500</v>
-      </c>
-      <c r="J15" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K15" s="5">
+      <c r="H15" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I15" s="3">
+        <v>500</v>
+      </c>
+      <c r="J15" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K15" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1811,19 +1782,19 @@
       <c r="D16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I16" s="5">
-        <v>500</v>
-      </c>
-      <c r="J16" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K16" s="5">
+      <c r="H16" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I16" s="3">
+        <v>500</v>
+      </c>
+      <c r="J16" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K16" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1840,19 +1811,19 @@
       <c r="D17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I17" s="5">
-        <v>500</v>
-      </c>
-      <c r="J17" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K17" s="5">
+      <c r="H17" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I17" s="3">
+        <v>500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K17" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1869,19 +1840,19 @@
       <c r="D18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I18" s="5">
-        <v>500</v>
-      </c>
-      <c r="J18" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K18" s="5">
+      <c r="H18" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I18" s="3">
+        <v>500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K18" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1898,19 +1869,19 @@
       <c r="D19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I19" s="5">
-        <v>500</v>
-      </c>
-      <c r="J19" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K19" s="5">
+      <c r="H19" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I19" s="3">
+        <v>500</v>
+      </c>
+      <c r="J19" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K19" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1927,19 +1898,19 @@
       <c r="D20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I20" s="5">
-        <v>500</v>
-      </c>
-      <c r="J20" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K20" s="5">
+      <c r="H20" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I20" s="3">
+        <v>500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K20" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1956,19 +1927,19 @@
       <c r="D21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I21" s="5">
-        <v>500</v>
-      </c>
-      <c r="J21" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K21" s="5">
+      <c r="H21" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I21" s="3">
+        <v>500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K21" s="3">
         <v>500</v>
       </c>
     </row>
@@ -1985,19 +1956,19 @@
       <c r="D22" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H22" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I22" s="5">
-        <v>500</v>
-      </c>
-      <c r="J22" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K22" s="5">
+      <c r="H22" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I22" s="3">
+        <v>500</v>
+      </c>
+      <c r="J22" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K22" s="3">
         <v>500</v>
       </c>
     </row>
@@ -2014,19 +1985,19 @@
       <c r="D23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I23" s="5">
-        <v>500</v>
-      </c>
-      <c r="J23" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K23" s="5">
+      <c r="H23" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I23" s="3">
+        <v>500</v>
+      </c>
+      <c r="J23" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K23" s="3">
         <v>500</v>
       </c>
     </row>
@@ -2043,19 +2014,19 @@
       <c r="D24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H24" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I24" s="5">
-        <v>500</v>
-      </c>
-      <c r="J24" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K24" s="5">
+      <c r="H24" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I24" s="3">
+        <v>500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K24" s="3">
         <v>500</v>
       </c>
     </row>
@@ -2072,19 +2043,19 @@
       <c r="D25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I25" s="5">
-        <v>500</v>
-      </c>
-      <c r="J25" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K25" s="5">
+      <c r="H25" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I25" s="3">
+        <v>500</v>
+      </c>
+      <c r="J25" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K25" s="3">
         <v>500</v>
       </c>
     </row>
@@ -2101,19 +2072,19 @@
       <c r="D26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H26" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I26" s="5">
-        <v>500</v>
-      </c>
-      <c r="J26" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K26" s="5">
+      <c r="H26" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I26" s="3">
+        <v>500</v>
+      </c>
+      <c r="J26" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K26" s="3">
         <v>500</v>
       </c>
     </row>
@@ -2130,19 +2101,19 @@
       <c r="D27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I27" s="5">
-        <v>500</v>
-      </c>
-      <c r="J27" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K27" s="5">
+      <c r="H27" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I27" s="3">
+        <v>500</v>
+      </c>
+      <c r="J27" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K27" s="3">
         <v>500</v>
       </c>
     </row>
@@ -2159,19 +2130,19 @@
       <c r="D28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H28" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I28" s="5">
-        <v>500</v>
-      </c>
-      <c r="J28" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K28" s="5">
+      <c r="H28" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I28" s="3">
+        <v>500</v>
+      </c>
+      <c r="J28" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K28" s="3">
         <v>500</v>
       </c>
     </row>
@@ -2188,19 +2159,19 @@
       <c r="D29" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H29" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I29" s="5">
-        <v>500</v>
-      </c>
-      <c r="J29" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K29" s="5">
+      <c r="H29" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I29" s="3">
+        <v>500</v>
+      </c>
+      <c r="J29" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K29" s="3">
         <v>500</v>
       </c>
     </row>
@@ -2217,19 +2188,19 @@
       <c r="D30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H30" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I30" s="5">
-        <v>500</v>
-      </c>
-      <c r="J30" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K30" s="5">
+      <c r="H30" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I30" s="3">
+        <v>500</v>
+      </c>
+      <c r="J30" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K30" s="3">
         <v>500</v>
       </c>
     </row>
@@ -2246,19 +2217,19 @@
       <c r="D31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I31" s="5">
-        <v>500</v>
-      </c>
-      <c r="J31" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K31" s="5">
+      <c r="H31" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I31" s="3">
+        <v>500</v>
+      </c>
+      <c r="J31" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K31" s="3">
         <v>500</v>
       </c>
     </row>
@@ -2275,19 +2246,19 @@
       <c r="D32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H32" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I32" s="5">
-        <v>500</v>
-      </c>
-      <c r="J32" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K32" s="5">
+      <c r="H32" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I32" s="3">
+        <v>500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K32" s="3">
         <v>500</v>
       </c>
     </row>
@@ -2304,19 +2275,19 @@
       <c r="D33" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H33" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I33" s="5">
-        <v>500</v>
-      </c>
-      <c r="J33" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K33" s="5">
+      <c r="H33" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I33" s="3">
+        <v>500</v>
+      </c>
+      <c r="J33" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K33" s="3">
         <v>500</v>
       </c>
     </row>
@@ -2333,27 +2304,26 @@
       <c r="D34" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H34" s="4">
-        <v>20250101</v>
-      </c>
-      <c r="I34" s="5">
-        <v>500</v>
-      </c>
-      <c r="J34" s="5">
-        <v>20250101</v>
-      </c>
-      <c r="K34" s="5">
+      <c r="H34" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="I34" s="3">
+        <v>500</v>
+      </c>
+      <c r="J34" s="3">
+        <v>20250101</v>
+      </c>
+      <c r="K34" s="3">
         <v>500</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:11">
-      <c r="F35" s="6"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="5"/>
+      <c r="F35" s="4"/>
+      <c r="I35" s="3"/>
+      <c r="K35" s="3"/>
     </row>
     <row r="37" s="2" customFormat="1" spans="1:11">
       <c r="A37" s="2">
@@ -2371,16 +2341,16 @@
       <c r="G37" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H37" s="9">
-        <v>20251120</v>
-      </c>
-      <c r="I37" s="10">
-        <v>500</v>
-      </c>
-      <c r="J37" s="9">
-        <v>20991124</v>
-      </c>
-      <c r="K37" s="10">
+      <c r="H37" s="6">
+        <v>20261120</v>
+      </c>
+      <c r="I37" s="7">
+        <v>500</v>
+      </c>
+      <c r="J37" s="6">
+        <v>20261124</v>
+      </c>
+      <c r="K37" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2400,16 +2370,16 @@
       <c r="G38" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H38" s="11">
+      <c r="H38" s="6">
         <v>20261211</v>
       </c>
-      <c r="I38" s="10">
-        <v>500</v>
-      </c>
-      <c r="J38" s="12">
+      <c r="I38" s="7">
+        <v>500</v>
+      </c>
+      <c r="J38" s="6">
         <v>20261215</v>
       </c>
-      <c r="K38" s="10">
+      <c r="K38" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2429,16 +2399,16 @@
       <c r="G39" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H39" s="11">
+      <c r="H39" s="6">
         <v>20270101</v>
       </c>
-      <c r="I39" s="10">
-        <v>500</v>
-      </c>
-      <c r="J39" s="12">
+      <c r="I39" s="7">
+        <v>500</v>
+      </c>
+      <c r="J39" s="6">
         <v>20270105</v>
       </c>
-      <c r="K39" s="10">
+      <c r="K39" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2458,16 +2428,16 @@
       <c r="G40" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H40" s="11">
+      <c r="H40" s="6">
         <v>20270122</v>
       </c>
-      <c r="I40" s="10">
-        <v>500</v>
-      </c>
-      <c r="J40" s="12">
+      <c r="I40" s="7">
+        <v>500</v>
+      </c>
+      <c r="J40" s="6">
         <v>20270126</v>
       </c>
-      <c r="K40" s="10">
+      <c r="K40" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2487,16 +2457,16 @@
       <c r="G41" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H41" s="6">
         <v>20270212</v>
       </c>
-      <c r="I41" s="10">
-        <v>500</v>
-      </c>
-      <c r="J41" s="12">
+      <c r="I41" s="7">
+        <v>500</v>
+      </c>
+      <c r="J41" s="6">
         <v>20270216</v>
       </c>
-      <c r="K41" s="10">
+      <c r="K41" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2516,16 +2486,16 @@
       <c r="G42" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H42" s="11">
+      <c r="H42" s="6">
         <v>20270305</v>
       </c>
-      <c r="I42" s="10">
-        <v>500</v>
-      </c>
-      <c r="J42" s="12">
+      <c r="I42" s="7">
+        <v>500</v>
+      </c>
+      <c r="J42" s="6">
         <v>20270309</v>
       </c>
-      <c r="K42" s="10">
+      <c r="K42" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2545,16 +2515,16 @@
       <c r="G44" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H44" s="9">
-        <v>20251106</v>
-      </c>
-      <c r="I44" s="10">
-        <v>500</v>
-      </c>
-      <c r="J44" s="9">
-        <v>20991110</v>
-      </c>
-      <c r="K44" s="10">
+      <c r="H44" s="6">
+        <v>20261106</v>
+      </c>
+      <c r="I44" s="7">
+        <v>500</v>
+      </c>
+      <c r="J44" s="6">
+        <v>20261110</v>
+      </c>
+      <c r="K44" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2574,16 +2544,16 @@
       <c r="G45" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H45" s="11">
+      <c r="H45" s="6">
         <v>20261113</v>
       </c>
-      <c r="I45" s="10">
-        <v>500</v>
-      </c>
-      <c r="J45" s="12">
+      <c r="I45" s="7">
+        <v>500</v>
+      </c>
+      <c r="J45" s="6">
         <v>20261117</v>
       </c>
-      <c r="K45" s="10">
+      <c r="K45" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2603,16 +2573,16 @@
       <c r="G46" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H46" s="11">
+      <c r="H46" s="6">
         <v>20261127</v>
       </c>
-      <c r="I46" s="10">
-        <v>500</v>
-      </c>
-      <c r="J46" s="12">
+      <c r="I46" s="7">
+        <v>500</v>
+      </c>
+      <c r="J46" s="6">
         <v>20261201</v>
       </c>
-      <c r="K46" s="10">
+      <c r="K46" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2632,16 +2602,16 @@
       <c r="G47" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="6">
         <v>20261204</v>
       </c>
-      <c r="I47" s="10">
-        <v>500</v>
-      </c>
-      <c r="J47" s="12">
+      <c r="I47" s="7">
+        <v>500</v>
+      </c>
+      <c r="J47" s="6">
         <v>20261208</v>
       </c>
-      <c r="K47" s="10">
+      <c r="K47" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2661,16 +2631,16 @@
       <c r="G48" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H48" s="11">
+      <c r="H48" s="6">
         <v>20261218</v>
       </c>
-      <c r="I48" s="10">
-        <v>500</v>
-      </c>
-      <c r="J48" s="12">
+      <c r="I48" s="7">
+        <v>500</v>
+      </c>
+      <c r="J48" s="6">
         <v>20261222</v>
       </c>
-      <c r="K48" s="10">
+      <c r="K48" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2690,16 +2660,16 @@
       <c r="G49" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H49" s="11">
+      <c r="H49" s="6">
         <v>20261225</v>
       </c>
-      <c r="I49" s="10">
-        <v>500</v>
-      </c>
-      <c r="J49" s="12">
+      <c r="I49" s="7">
+        <v>500</v>
+      </c>
+      <c r="J49" s="6">
         <v>20261229</v>
       </c>
-      <c r="K49" s="10">
+      <c r="K49" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2719,16 +2689,16 @@
       <c r="G51" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H51" s="13">
+      <c r="H51" s="8">
         <v>20270108</v>
       </c>
-      <c r="I51" s="10">
-        <v>500</v>
-      </c>
-      <c r="J51" s="14">
+      <c r="I51" s="7">
+        <v>500</v>
+      </c>
+      <c r="J51" s="8">
         <v>20270112</v>
       </c>
-      <c r="K51" s="10">
+      <c r="K51" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2748,16 +2718,16 @@
       <c r="G52" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52" s="6">
         <v>20270115</v>
       </c>
-      <c r="I52" s="10">
-        <v>500</v>
-      </c>
-      <c r="J52" s="12">
+      <c r="I52" s="7">
+        <v>500</v>
+      </c>
+      <c r="J52" s="6">
         <v>20270119</v>
       </c>
-      <c r="K52" s="10">
+      <c r="K52" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2777,16 +2747,16 @@
       <c r="G53" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H53" s="11">
+      <c r="H53" s="6">
         <v>20270129</v>
       </c>
-      <c r="I53" s="10">
-        <v>500</v>
-      </c>
-      <c r="J53" s="12">
+      <c r="I53" s="7">
+        <v>500</v>
+      </c>
+      <c r="J53" s="6">
         <v>20270202</v>
       </c>
-      <c r="K53" s="10">
+      <c r="K53" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2806,16 +2776,16 @@
       <c r="G54" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H54" s="11">
+      <c r="H54" s="6">
         <v>20270205</v>
       </c>
-      <c r="I54" s="10">
-        <v>500</v>
-      </c>
-      <c r="J54" s="12">
+      <c r="I54" s="7">
+        <v>500</v>
+      </c>
+      <c r="J54" s="6">
         <v>20270209</v>
       </c>
-      <c r="K54" s="10">
+      <c r="K54" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2835,16 +2805,16 @@
       <c r="G55" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H55" s="11">
+      <c r="H55" s="6">
         <v>20270219</v>
       </c>
-      <c r="I55" s="10">
-        <v>500</v>
-      </c>
-      <c r="J55" s="12">
+      <c r="I55" s="7">
+        <v>500</v>
+      </c>
+      <c r="J55" s="6">
         <v>20270223</v>
       </c>
-      <c r="K55" s="10">
+      <c r="K55" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2864,16 +2834,16 @@
       <c r="G56" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H56" s="11">
+      <c r="H56" s="6">
         <v>20270226</v>
       </c>
-      <c r="I56" s="10">
-        <v>500</v>
-      </c>
-      <c r="J56" s="12">
+      <c r="I56" s="7">
+        <v>500</v>
+      </c>
+      <c r="J56" s="6">
         <v>20270302</v>
       </c>
-      <c r="K56" s="10">
+      <c r="K56" s="7">
         <v>500</v>
       </c>
     </row>
@@ -2893,16 +2863,16 @@
       <c r="G58" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H58" s="7">
+      <c r="H58" s="5">
         <v>20270312</v>
       </c>
-      <c r="I58" s="15">
-        <v>500</v>
-      </c>
-      <c r="J58" s="8">
+      <c r="I58" s="9">
+        <v>500</v>
+      </c>
+      <c r="J58" s="5">
         <v>20270316</v>
       </c>
-      <c r="K58" s="15">
+      <c r="K58" s="9">
         <v>500</v>
       </c>
     </row>
@@ -2922,16 +2892,16 @@
       <c r="G59" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H59" s="7">
+      <c r="H59" s="5">
         <v>20270319</v>
       </c>
-      <c r="I59" s="15">
-        <v>500</v>
-      </c>
-      <c r="J59" s="8">
+      <c r="I59" s="9">
+        <v>500</v>
+      </c>
+      <c r="J59" s="5">
         <v>20270323</v>
       </c>
-      <c r="K59" s="15">
+      <c r="K59" s="9">
         <v>500</v>
       </c>
     </row>
@@ -2951,16 +2921,16 @@
       <c r="G60" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H60" s="7">
+      <c r="H60" s="5">
         <v>20270402</v>
       </c>
-      <c r="I60" s="15">
-        <v>500</v>
-      </c>
-      <c r="J60" s="8">
+      <c r="I60" s="9">
+        <v>500</v>
+      </c>
+      <c r="J60" s="5">
         <v>20270406</v>
       </c>
-      <c r="K60" s="15">
+      <c r="K60" s="9">
         <v>500</v>
       </c>
     </row>
@@ -2980,16 +2950,16 @@
       <c r="G61" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H61" s="7">
+      <c r="H61" s="5">
         <v>20270409</v>
       </c>
-      <c r="I61" s="15">
-        <v>500</v>
-      </c>
-      <c r="J61" s="16">
+      <c r="I61" s="9">
+        <v>500</v>
+      </c>
+      <c r="J61" s="10">
         <v>20270413</v>
       </c>
-      <c r="K61" s="15">
+      <c r="K61" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3009,16 +2979,16 @@
       <c r="G62" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H62" s="7">
+      <c r="H62" s="5">
         <v>20270423</v>
       </c>
-      <c r="I62" s="15">
-        <v>500</v>
-      </c>
-      <c r="J62" s="8">
+      <c r="I62" s="9">
+        <v>500</v>
+      </c>
+      <c r="J62" s="5">
         <v>20270427</v>
       </c>
-      <c r="K62" s="15">
+      <c r="K62" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3038,23 +3008,22 @@
       <c r="G63" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H63" s="7">
+      <c r="H63" s="5">
         <v>20270430</v>
       </c>
-      <c r="I63" s="15">
-        <v>500</v>
-      </c>
-      <c r="J63" s="8">
+      <c r="I63" s="9">
+        <v>500</v>
+      </c>
+      <c r="J63" s="5">
         <v>20270504</v>
       </c>
-      <c r="K63" s="15">
+      <c r="K63" s="9">
         <v>500</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" spans="1:11">
-      <c r="I64" s="5"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="5"/>
+      <c r="I64" s="3"/>
+      <c r="K64" s="3"/>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:11">
       <c r="A65" s="1">
@@ -3072,16 +3041,16 @@
       <c r="G65" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H65" s="7">
+      <c r="H65" s="5">
         <v>20270326</v>
       </c>
-      <c r="I65" s="15">
-        <v>500</v>
-      </c>
-      <c r="J65" s="8">
+      <c r="I65" s="9">
+        <v>500</v>
+      </c>
+      <c r="J65" s="5">
         <v>20270330</v>
       </c>
-      <c r="K65" s="15">
+      <c r="K65" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3101,16 +3070,16 @@
       <c r="G66" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H66" s="7">
+      <c r="H66" s="5">
         <v>20270416</v>
       </c>
-      <c r="I66" s="15">
-        <v>500</v>
-      </c>
-      <c r="J66" s="8">
+      <c r="I66" s="9">
+        <v>500</v>
+      </c>
+      <c r="J66" s="5">
         <v>20270420</v>
       </c>
-      <c r="K66" s="15">
+      <c r="K66" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3130,16 +3099,16 @@
       <c r="G67" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H67" s="7">
+      <c r="H67" s="5">
         <v>20270507</v>
       </c>
-      <c r="I67" s="15">
-        <v>500</v>
-      </c>
-      <c r="J67" s="8">
+      <c r="I67" s="9">
+        <v>500</v>
+      </c>
+      <c r="J67" s="5">
         <v>20270511</v>
       </c>
-      <c r="K67" s="15">
+      <c r="K67" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3159,16 +3128,16 @@
       <c r="G68" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H68" s="7">
+      <c r="H68" s="5">
         <v>20270528</v>
       </c>
-      <c r="I68" s="15">
-        <v>500</v>
-      </c>
-      <c r="J68" s="8">
+      <c r="I68" s="9">
+        <v>500</v>
+      </c>
+      <c r="J68" s="5">
         <v>20270601</v>
       </c>
-      <c r="K68" s="15">
+      <c r="K68" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3188,16 +3157,16 @@
       <c r="G69" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H69" s="7">
+      <c r="H69" s="5">
         <v>20270618</v>
       </c>
-      <c r="I69" s="15">
-        <v>500</v>
-      </c>
-      <c r="J69" s="8">
+      <c r="I69" s="9">
+        <v>500</v>
+      </c>
+      <c r="J69" s="5">
         <v>20270622</v>
       </c>
-      <c r="K69" s="15">
+      <c r="K69" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3217,23 +3186,22 @@
       <c r="G70" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H70" s="7">
+      <c r="H70" s="5">
         <v>20270709</v>
       </c>
-      <c r="I70" s="15">
-        <v>500</v>
-      </c>
-      <c r="J70" s="8">
+      <c r="I70" s="9">
+        <v>500</v>
+      </c>
+      <c r="J70" s="5">
         <v>20270713</v>
       </c>
-      <c r="K70" s="15">
+      <c r="K70" s="9">
         <v>500</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:11">
-      <c r="I71" s="5"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="5"/>
+      <c r="I71" s="3"/>
+      <c r="K71" s="3"/>
     </row>
     <row r="72" s="1" customFormat="1" spans="1:11">
       <c r="A72" s="1">
@@ -3251,16 +3219,16 @@
       <c r="G72" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H72" s="17">
+      <c r="H72" s="11">
         <v>20270604</v>
       </c>
-      <c r="I72" s="15">
-        <v>500</v>
-      </c>
-      <c r="J72" s="18">
+      <c r="I72" s="9">
+        <v>500</v>
+      </c>
+      <c r="J72" s="11">
         <v>20270704</v>
       </c>
-      <c r="K72" s="15">
+      <c r="K72" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3280,16 +3248,16 @@
       <c r="G73" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H73" s="17">
+      <c r="H73" s="11">
         <v>20270430</v>
       </c>
-      <c r="I73" s="15">
-        <v>500</v>
-      </c>
-      <c r="J73" s="18">
+      <c r="I73" s="9">
+        <v>500</v>
+      </c>
+      <c r="J73" s="11">
         <v>20270603</v>
       </c>
-      <c r="K73" s="15">
+      <c r="K73" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3309,16 +3277,16 @@
       <c r="G74" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H74" s="17">
+      <c r="H74" s="11">
         <v>20270325</v>
       </c>
-      <c r="I74" s="15">
-        <v>500</v>
-      </c>
-      <c r="J74" s="18">
+      <c r="I74" s="9">
+        <v>500</v>
+      </c>
+      <c r="J74" s="11">
         <v>20270429</v>
       </c>
-      <c r="K74" s="15">
+      <c r="K74" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3338,16 +3306,16 @@
       <c r="G75" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H75" s="17">
+      <c r="H75" s="11">
         <v>20270221</v>
       </c>
-      <c r="I75" s="15">
-        <v>500</v>
-      </c>
-      <c r="J75" s="18">
+      <c r="I75" s="9">
+        <v>500</v>
+      </c>
+      <c r="J75" s="11">
         <v>20270324</v>
       </c>
-      <c r="K75" s="15">
+      <c r="K75" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3367,16 +3335,16 @@
       <c r="G76" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H76" s="17">
+      <c r="H76" s="11">
         <v>20270117</v>
       </c>
-      <c r="I76" s="15">
-        <v>500</v>
-      </c>
-      <c r="J76" s="18">
+      <c r="I76" s="9">
+        <v>500</v>
+      </c>
+      <c r="J76" s="11">
         <v>20270220</v>
       </c>
-      <c r="K76" s="15">
+      <c r="K76" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3396,16 +3364,16 @@
       <c r="G77" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H77" s="17">
+      <c r="H77" s="11">
         <v>20261212</v>
       </c>
-      <c r="I77" s="15">
-        <v>500</v>
-      </c>
-      <c r="J77" s="18">
+      <c r="I77" s="9">
+        <v>500</v>
+      </c>
+      <c r="J77" s="11">
         <v>20270116</v>
       </c>
-      <c r="K77" s="15">
+      <c r="K77" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3425,16 +3393,16 @@
       <c r="G78" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H78" s="19">
-        <v>20251113</v>
-      </c>
-      <c r="I78" s="15">
-        <v>500</v>
-      </c>
-      <c r="J78" s="19">
-        <v>20991211</v>
-      </c>
-      <c r="K78" s="15">
+      <c r="H78" s="11">
+        <v>20261113</v>
+      </c>
+      <c r="I78" s="9">
+        <v>500</v>
+      </c>
+      <c r="J78" s="11">
+        <v>20261211</v>
+      </c>
+      <c r="K78" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3454,16 +3422,16 @@
       <c r="G81" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H81" s="7">
+      <c r="H81" s="5">
         <v>20270514</v>
       </c>
-      <c r="I81" s="15">
-        <v>500</v>
-      </c>
-      <c r="J81" s="8">
+      <c r="I81" s="9">
+        <v>500</v>
+      </c>
+      <c r="J81" s="5">
         <v>20270518</v>
       </c>
-      <c r="K81" s="15">
+      <c r="K81" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3483,16 +3451,16 @@
       <c r="G82" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H82" s="7">
+      <c r="H82" s="5">
         <v>20270521</v>
       </c>
-      <c r="I82" s="15">
-        <v>500</v>
-      </c>
-      <c r="J82" s="8">
+      <c r="I82" s="9">
+        <v>500</v>
+      </c>
+      <c r="J82" s="5">
         <v>20270525</v>
       </c>
-      <c r="K82" s="15">
+      <c r="K82" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3512,16 +3480,16 @@
       <c r="G83" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H83" s="7">
+      <c r="H83" s="5">
         <v>20270604</v>
       </c>
-      <c r="I83" s="15">
-        <v>500</v>
-      </c>
-      <c r="J83" s="8">
+      <c r="I83" s="9">
+        <v>500</v>
+      </c>
+      <c r="J83" s="5">
         <v>20270608</v>
       </c>
-      <c r="K83" s="15">
+      <c r="K83" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3541,16 +3509,16 @@
       <c r="G84" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H84" s="7">
+      <c r="H84" s="5">
         <v>20270611</v>
       </c>
-      <c r="I84" s="15">
-        <v>500</v>
-      </c>
-      <c r="J84" s="8">
+      <c r="I84" s="9">
+        <v>500</v>
+      </c>
+      <c r="J84" s="5">
         <v>20270615</v>
       </c>
-      <c r="K84" s="15">
+      <c r="K84" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3570,16 +3538,16 @@
       <c r="G85" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H85" s="7">
+      <c r="H85" s="5">
         <v>20270625</v>
       </c>
-      <c r="I85" s="15">
-        <v>500</v>
-      </c>
-      <c r="J85" s="8">
+      <c r="I85" s="9">
+        <v>500</v>
+      </c>
+      <c r="J85" s="5">
         <v>20270629</v>
       </c>
-      <c r="K85" s="15">
+      <c r="K85" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3599,28 +3567,26 @@
       <c r="G86" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H86" s="7">
+      <c r="H86" s="5">
         <v>20270702</v>
       </c>
-      <c r="I86" s="15">
-        <v>500</v>
-      </c>
-      <c r="J86" s="8">
+      <c r="I86" s="9">
+        <v>500</v>
+      </c>
+      <c r="J86" s="5">
         <v>20270706</v>
       </c>
-      <c r="K86" s="15">
+      <c r="K86" s="9">
         <v>500</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" spans="1:11">
-      <c r="I88" s="5"/>
-      <c r="J88" s="3"/>
-      <c r="K88" s="5"/>
+      <c r="I88" s="3"/>
+      <c r="K88" s="3"/>
     </row>
     <row r="89" s="1" customFormat="1" spans="1:11">
-      <c r="I89" s="5"/>
-      <c r="J89" s="3"/>
-      <c r="K89" s="5"/>
+      <c r="I89" s="3"/>
+      <c r="K89" s="3"/>
     </row>
     <row r="90" s="1" customFormat="1" spans="1:11">
       <c r="A90" s="1">
@@ -3638,16 +3604,16 @@
       <c r="G90" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H90" s="7">
+      <c r="H90" s="5">
         <v>20270716</v>
       </c>
-      <c r="I90" s="15">
-        <v>500</v>
-      </c>
-      <c r="J90" s="8">
+      <c r="I90" s="9">
+        <v>500</v>
+      </c>
+      <c r="J90" s="5">
         <v>20270720</v>
       </c>
-      <c r="K90" s="15">
+      <c r="K90" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3667,16 +3633,16 @@
       <c r="G91" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H91" s="7">
+      <c r="H91" s="5">
         <v>20270723</v>
       </c>
-      <c r="I91" s="15">
-        <v>500</v>
-      </c>
-      <c r="J91" s="8">
+      <c r="I91" s="9">
+        <v>500</v>
+      </c>
+      <c r="J91" s="5">
         <v>20270727</v>
       </c>
-      <c r="K91" s="15">
+      <c r="K91" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3696,16 +3662,16 @@
       <c r="G92" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H92" s="7">
+      <c r="H92" s="5">
         <v>20270806</v>
       </c>
-      <c r="I92" s="15">
-        <v>500</v>
-      </c>
-      <c r="J92" s="8">
+      <c r="I92" s="9">
+        <v>500</v>
+      </c>
+      <c r="J92" s="5">
         <v>20270810</v>
       </c>
-      <c r="K92" s="15">
+      <c r="K92" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3725,16 +3691,16 @@
       <c r="G93" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H93" s="7">
+      <c r="H93" s="5">
         <v>20270813</v>
       </c>
-      <c r="I93" s="15">
-        <v>500</v>
-      </c>
-      <c r="J93" s="8">
+      <c r="I93" s="9">
+        <v>500</v>
+      </c>
+      <c r="J93" s="5">
         <v>20270817</v>
       </c>
-      <c r="K93" s="15">
+      <c r="K93" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3754,16 +3720,16 @@
       <c r="G94" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H94" s="7">
+      <c r="H94" s="5">
         <v>20270827</v>
       </c>
-      <c r="I94" s="15">
-        <v>500</v>
-      </c>
-      <c r="J94" s="8">
+      <c r="I94" s="9">
+        <v>500</v>
+      </c>
+      <c r="J94" s="5">
         <v>20270831</v>
       </c>
-      <c r="K94" s="15">
+      <c r="K94" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3783,23 +3749,22 @@
       <c r="G95" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H95" s="7">
+      <c r="H95" s="5">
         <v>20270903</v>
       </c>
-      <c r="I95" s="15">
-        <v>500</v>
-      </c>
-      <c r="J95" s="8">
+      <c r="I95" s="9">
+        <v>500</v>
+      </c>
+      <c r="J95" s="5">
         <v>20270907</v>
       </c>
-      <c r="K95" s="15">
+      <c r="K95" s="9">
         <v>500</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="1:11">
-      <c r="I98" s="5"/>
-      <c r="J98" s="3"/>
-      <c r="K98" s="5"/>
+      <c r="I98" s="3"/>
+      <c r="K98" s="3"/>
     </row>
     <row r="99" s="1" customFormat="1" spans="1:11">
       <c r="A99" s="1">
@@ -3817,16 +3782,16 @@
       <c r="G99" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H99" s="7">
+      <c r="H99" s="5">
         <v>20270917</v>
       </c>
-      <c r="I99" s="15">
-        <v>500</v>
-      </c>
-      <c r="J99" s="8">
+      <c r="I99" s="9">
+        <v>500</v>
+      </c>
+      <c r="J99" s="5">
         <v>20270921</v>
       </c>
-      <c r="K99" s="15">
+      <c r="K99" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3846,16 +3811,16 @@
       <c r="G100" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H100" s="7">
+      <c r="H100" s="5">
         <v>20270924</v>
       </c>
-      <c r="I100" s="15">
-        <v>500</v>
-      </c>
-      <c r="J100" s="8">
+      <c r="I100" s="9">
+        <v>500</v>
+      </c>
+      <c r="J100" s="5">
         <v>20270928</v>
       </c>
-      <c r="K100" s="15">
+      <c r="K100" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3875,16 +3840,16 @@
       <c r="G101" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H101" s="7">
+      <c r="H101" s="5">
         <v>20271008</v>
       </c>
-      <c r="I101" s="15">
-        <v>500</v>
-      </c>
-      <c r="J101" s="8">
+      <c r="I101" s="9">
+        <v>500</v>
+      </c>
+      <c r="J101" s="5">
         <v>20271012</v>
       </c>
-      <c r="K101" s="15">
+      <c r="K101" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3904,16 +3869,16 @@
       <c r="G102" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H102" s="7">
+      <c r="H102" s="5">
         <v>20271015</v>
       </c>
-      <c r="I102" s="15">
-        <v>500</v>
-      </c>
-      <c r="J102" s="8">
+      <c r="I102" s="9">
+        <v>500</v>
+      </c>
+      <c r="J102" s="5">
         <v>20271019</v>
       </c>
-      <c r="K102" s="15">
+      <c r="K102" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3933,16 +3898,16 @@
       <c r="G103" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H103" s="7">
+      <c r="H103" s="5">
         <v>20271029</v>
       </c>
-      <c r="I103" s="15">
-        <v>500</v>
-      </c>
-      <c r="J103" s="8">
+      <c r="I103" s="9">
+        <v>500</v>
+      </c>
+      <c r="J103" s="5">
         <v>20271102</v>
       </c>
-      <c r="K103" s="15">
+      <c r="K103" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3962,16 +3927,16 @@
       <c r="G104" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H104" s="7">
+      <c r="H104" s="5">
         <v>20271105</v>
       </c>
-      <c r="I104" s="15">
-        <v>500</v>
-      </c>
-      <c r="J104" s="8">
+      <c r="I104" s="9">
+        <v>500</v>
+      </c>
+      <c r="J104" s="5">
         <v>20271109</v>
       </c>
-      <c r="K104" s="15">
+      <c r="K104" s="9">
         <v>500</v>
       </c>
     </row>
@@ -3991,16 +3956,16 @@
       <c r="G108" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H108" s="7">
+      <c r="H108" s="5">
         <v>20271119</v>
       </c>
-      <c r="I108" s="15">
-        <v>500</v>
-      </c>
-      <c r="J108" s="8">
+      <c r="I108" s="9">
+        <v>500</v>
+      </c>
+      <c r="J108" s="5">
         <v>20271123</v>
       </c>
-      <c r="K108" s="15">
+      <c r="K108" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4020,16 +3985,16 @@
       <c r="G109" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H109" s="7">
+      <c r="H109" s="5">
         <v>20271126</v>
       </c>
-      <c r="I109" s="15">
-        <v>500</v>
-      </c>
-      <c r="J109" s="8">
+      <c r="I109" s="9">
+        <v>500</v>
+      </c>
+      <c r="J109" s="5">
         <v>20271130</v>
       </c>
-      <c r="K109" s="15">
+      <c r="K109" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4049,16 +4014,16 @@
       <c r="G110" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H110" s="7">
+      <c r="H110" s="5">
         <v>20271210</v>
       </c>
-      <c r="I110" s="15">
-        <v>500</v>
-      </c>
-      <c r="J110" s="8">
+      <c r="I110" s="9">
+        <v>500</v>
+      </c>
+      <c r="J110" s="5">
         <v>20271214</v>
       </c>
-      <c r="K110" s="15">
+      <c r="K110" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4078,16 +4043,16 @@
       <c r="G111" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H111" s="7">
+      <c r="H111" s="5">
         <v>20271217</v>
       </c>
-      <c r="I111" s="15">
-        <v>500</v>
-      </c>
-      <c r="J111" s="8">
+      <c r="I111" s="9">
+        <v>500</v>
+      </c>
+      <c r="J111" s="5">
         <v>20271221</v>
       </c>
-      <c r="K111" s="15">
+      <c r="K111" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4107,16 +4072,16 @@
       <c r="G112" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H112" s="7">
+      <c r="H112" s="5">
         <v>20271231</v>
       </c>
-      <c r="I112" s="15">
-        <v>500</v>
-      </c>
-      <c r="J112" s="8">
+      <c r="I112" s="9">
+        <v>500</v>
+      </c>
+      <c r="J112" s="5">
         <v>20280104</v>
       </c>
-      <c r="K112" s="15">
+      <c r="K112" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4136,16 +4101,16 @@
       <c r="G113" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H113" s="7">
+      <c r="H113" s="5">
         <v>20280107</v>
       </c>
-      <c r="I113" s="15">
-        <v>500</v>
-      </c>
-      <c r="J113" s="8">
+      <c r="I113" s="9">
+        <v>500</v>
+      </c>
+      <c r="J113" s="5">
         <v>20280111</v>
       </c>
-      <c r="K113" s="15">
+      <c r="K113" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4165,16 +4130,16 @@
       <c r="G117" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H117" s="7">
+      <c r="H117" s="5">
         <v>20280121</v>
       </c>
-      <c r="I117" s="15">
-        <v>500</v>
-      </c>
-      <c r="J117" s="8">
+      <c r="I117" s="9">
+        <v>500</v>
+      </c>
+      <c r="J117" s="5">
         <v>20280125</v>
       </c>
-      <c r="K117" s="15">
+      <c r="K117" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4194,16 +4159,16 @@
       <c r="G118" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H118" s="7">
+      <c r="H118" s="5">
         <v>20280128</v>
       </c>
-      <c r="I118" s="15">
-        <v>500</v>
-      </c>
-      <c r="J118" s="8">
+      <c r="I118" s="9">
+        <v>500</v>
+      </c>
+      <c r="J118" s="5">
         <v>20280201</v>
       </c>
-      <c r="K118" s="15">
+      <c r="K118" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4223,16 +4188,16 @@
       <c r="G119" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H119" s="7">
+      <c r="H119" s="5">
         <v>20280211</v>
       </c>
-      <c r="I119" s="15">
-        <v>500</v>
-      </c>
-      <c r="J119" s="8">
+      <c r="I119" s="9">
+        <v>500</v>
+      </c>
+      <c r="J119" s="5">
         <v>20280215</v>
       </c>
-      <c r="K119" s="15">
+      <c r="K119" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4252,16 +4217,16 @@
       <c r="G120" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H120" s="7">
+      <c r="H120" s="5">
         <v>20280218</v>
       </c>
-      <c r="I120" s="15">
-        <v>500</v>
-      </c>
-      <c r="J120" s="8">
+      <c r="I120" s="9">
+        <v>500</v>
+      </c>
+      <c r="J120" s="5">
         <v>20280222</v>
       </c>
-      <c r="K120" s="15">
+      <c r="K120" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4281,16 +4246,16 @@
       <c r="G121" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H121" s="7">
+      <c r="H121" s="5">
         <v>20280303</v>
       </c>
-      <c r="I121" s="15">
-        <v>500</v>
-      </c>
-      <c r="J121" s="8">
+      <c r="I121" s="9">
+        <v>500</v>
+      </c>
+      <c r="J121" s="5">
         <v>20280307</v>
       </c>
-      <c r="K121" s="15">
+      <c r="K121" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4310,16 +4275,16 @@
       <c r="G122" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H122" s="7">
+      <c r="H122" s="5">
         <v>20280310</v>
       </c>
-      <c r="I122" s="15">
-        <v>500</v>
-      </c>
-      <c r="J122" s="8">
+      <c r="I122" s="9">
+        <v>500</v>
+      </c>
+      <c r="J122" s="5">
         <v>20280314</v>
       </c>
-      <c r="K122" s="15">
+      <c r="K122" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4339,16 +4304,16 @@
       <c r="G126" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H126" s="7">
+      <c r="H126" s="5">
         <v>20280324</v>
       </c>
-      <c r="I126" s="15">
-        <v>500</v>
-      </c>
-      <c r="J126" s="8">
+      <c r="I126" s="9">
+        <v>500</v>
+      </c>
+      <c r="J126" s="5">
         <v>20280328</v>
       </c>
-      <c r="K126" s="15">
+      <c r="K126" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4368,16 +4333,16 @@
       <c r="G127" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H127" s="7">
+      <c r="H127" s="5">
         <v>20280331</v>
       </c>
-      <c r="I127" s="15">
-        <v>500</v>
-      </c>
-      <c r="J127" s="8">
+      <c r="I127" s="9">
+        <v>500</v>
+      </c>
+      <c r="J127" s="5">
         <v>20280404</v>
       </c>
-      <c r="K127" s="15">
+      <c r="K127" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4397,16 +4362,16 @@
       <c r="G128" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H128" s="7">
+      <c r="H128" s="5">
         <v>20280414</v>
       </c>
-      <c r="I128" s="15">
-        <v>500</v>
-      </c>
-      <c r="J128" s="8">
+      <c r="I128" s="9">
+        <v>500</v>
+      </c>
+      <c r="J128" s="5">
         <v>20280418</v>
       </c>
-      <c r="K128" s="15">
+      <c r="K128" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4426,16 +4391,16 @@
       <c r="G129" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H129" s="7">
+      <c r="H129" s="5">
         <v>20280421</v>
       </c>
-      <c r="I129" s="15">
-        <v>500</v>
-      </c>
-      <c r="J129" s="8">
+      <c r="I129" s="9">
+        <v>500</v>
+      </c>
+      <c r="J129" s="5">
         <v>20280425</v>
       </c>
-      <c r="K129" s="15">
+      <c r="K129" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4455,16 +4420,16 @@
       <c r="G130" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H130" s="7">
+      <c r="H130" s="5">
         <v>20280505</v>
       </c>
-      <c r="I130" s="15">
-        <v>500</v>
-      </c>
-      <c r="J130" s="8">
+      <c r="I130" s="9">
+        <v>500</v>
+      </c>
+      <c r="J130" s="5">
         <v>20280509</v>
       </c>
-      <c r="K130" s="15">
+      <c r="K130" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4484,16 +4449,16 @@
       <c r="G131" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H131" s="7">
+      <c r="H131" s="5">
         <v>20280512</v>
       </c>
-      <c r="I131" s="15">
-        <v>500</v>
-      </c>
-      <c r="J131" s="8">
+      <c r="I131" s="9">
+        <v>500</v>
+      </c>
+      <c r="J131" s="5">
         <v>20280516</v>
       </c>
-      <c r="K131" s="15">
+      <c r="K131" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4513,16 +4478,16 @@
       <c r="G135" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H135" s="7">
+      <c r="H135" s="5">
         <v>20270730</v>
       </c>
-      <c r="I135" s="15">
-        <v>500</v>
-      </c>
-      <c r="J135" s="8">
+      <c r="I135" s="9">
+        <v>500</v>
+      </c>
+      <c r="J135" s="5">
         <v>20270803</v>
       </c>
-      <c r="K135" s="15">
+      <c r="K135" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4542,16 +4507,16 @@
       <c r="G136" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H136" s="7">
+      <c r="H136" s="5">
         <v>20270820</v>
       </c>
-      <c r="I136" s="15">
-        <v>500</v>
-      </c>
-      <c r="J136" s="8">
+      <c r="I136" s="9">
+        <v>500</v>
+      </c>
+      <c r="J136" s="5">
         <v>20270824</v>
       </c>
-      <c r="K136" s="15">
+      <c r="K136" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4571,16 +4536,16 @@
       <c r="G137" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H137" s="7">
+      <c r="H137" s="5">
         <v>20270910</v>
       </c>
-      <c r="I137" s="15">
-        <v>500</v>
-      </c>
-      <c r="J137" s="8">
+      <c r="I137" s="9">
+        <v>500</v>
+      </c>
+      <c r="J137" s="5">
         <v>20270914</v>
       </c>
-      <c r="K137" s="15">
+      <c r="K137" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4600,16 +4565,16 @@
       <c r="G138" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H138" s="7">
+      <c r="H138" s="5">
         <v>20271001</v>
       </c>
-      <c r="I138" s="15">
-        <v>500</v>
-      </c>
-      <c r="J138" s="8">
+      <c r="I138" s="9">
+        <v>500</v>
+      </c>
+      <c r="J138" s="5">
         <v>20271005</v>
       </c>
-      <c r="K138" s="15">
+      <c r="K138" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4629,16 +4594,16 @@
       <c r="G139" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H139" s="7">
+      <c r="H139" s="5">
         <v>20271022</v>
       </c>
-      <c r="I139" s="15">
-        <v>500</v>
-      </c>
-      <c r="J139" s="8">
+      <c r="I139" s="9">
+        <v>500</v>
+      </c>
+      <c r="J139" s="5">
         <v>20271026</v>
       </c>
-      <c r="K139" s="15">
+      <c r="K139" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4658,16 +4623,16 @@
       <c r="G140" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H140" s="7">
+      <c r="H140" s="5">
         <v>20271112</v>
       </c>
-      <c r="I140" s="15">
-        <v>500</v>
-      </c>
-      <c r="J140" s="8">
+      <c r="I140" s="9">
+        <v>500</v>
+      </c>
+      <c r="J140" s="5">
         <v>20271116</v>
       </c>
-      <c r="K140" s="15">
+      <c r="K140" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4687,16 +4652,16 @@
       <c r="G144" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H144" s="7">
+      <c r="H144" s="5">
         <v>20271203</v>
       </c>
-      <c r="I144" s="15">
-        <v>500</v>
-      </c>
-      <c r="J144" s="8">
+      <c r="I144" s="9">
+        <v>500</v>
+      </c>
+      <c r="J144" s="5">
         <v>20271207</v>
       </c>
-      <c r="K144" s="15">
+      <c r="K144" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4716,16 +4681,16 @@
       <c r="G145" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H145" s="7">
+      <c r="H145" s="5">
         <v>20271224</v>
       </c>
-      <c r="I145" s="15">
-        <v>500</v>
-      </c>
-      <c r="J145" s="8">
+      <c r="I145" s="9">
+        <v>500</v>
+      </c>
+      <c r="J145" s="5">
         <v>20271228</v>
       </c>
-      <c r="K145" s="15">
+      <c r="K145" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4745,16 +4710,16 @@
       <c r="G146" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H146" s="7">
+      <c r="H146" s="5">
         <v>20280114</v>
       </c>
-      <c r="I146" s="15">
-        <v>500</v>
-      </c>
-      <c r="J146" s="8">
+      <c r="I146" s="9">
+        <v>500</v>
+      </c>
+      <c r="J146" s="5">
         <v>20280118</v>
       </c>
-      <c r="K146" s="15">
+      <c r="K146" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4774,16 +4739,16 @@
       <c r="G147" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H147" s="7">
+      <c r="H147" s="5">
         <v>20280204</v>
       </c>
-      <c r="I147" s="15">
-        <v>500</v>
-      </c>
-      <c r="J147" s="8">
+      <c r="I147" s="9">
+        <v>500</v>
+      </c>
+      <c r="J147" s="5">
         <v>20280208</v>
       </c>
-      <c r="K147" s="15">
+      <c r="K147" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4803,16 +4768,16 @@
       <c r="G148" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H148" s="7">
+      <c r="H148" s="5">
         <v>20280225</v>
       </c>
-      <c r="I148" s="15">
-        <v>500</v>
-      </c>
-      <c r="J148" s="8">
+      <c r="I148" s="9">
+        <v>500</v>
+      </c>
+      <c r="J148" s="5">
         <v>20280229</v>
       </c>
-      <c r="K148" s="15">
+      <c r="K148" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4832,16 +4797,16 @@
       <c r="G149" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H149" s="7">
+      <c r="H149" s="5">
         <v>20280317</v>
       </c>
-      <c r="I149" s="15">
-        <v>500</v>
-      </c>
-      <c r="J149" s="8">
+      <c r="I149" s="9">
+        <v>500</v>
+      </c>
+      <c r="J149" s="5">
         <v>20280321</v>
       </c>
-      <c r="K149" s="15">
+      <c r="K149" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4861,16 +4826,16 @@
       <c r="G153" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H153" s="7">
+      <c r="H153" s="5">
         <v>20280407</v>
       </c>
-      <c r="I153" s="15">
-        <v>500</v>
-      </c>
-      <c r="J153" s="8">
+      <c r="I153" s="9">
+        <v>500</v>
+      </c>
+      <c r="J153" s="5">
         <v>20280411</v>
       </c>
-      <c r="K153" s="15">
+      <c r="K153" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4890,16 +4855,16 @@
       <c r="G154" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H154" s="7">
+      <c r="H154" s="5">
         <v>20280428</v>
       </c>
-      <c r="I154" s="15">
-        <v>500</v>
-      </c>
-      <c r="J154" s="8">
+      <c r="I154" s="9">
+        <v>500</v>
+      </c>
+      <c r="J154" s="5">
         <v>20280502</v>
       </c>
-      <c r="K154" s="15">
+      <c r="K154" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4919,16 +4884,16 @@
       <c r="G155" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H155" s="7">
+      <c r="H155" s="5">
         <v>20280519</v>
       </c>
-      <c r="I155" s="15">
-        <v>500</v>
-      </c>
-      <c r="J155" s="8">
+      <c r="I155" s="9">
+        <v>500</v>
+      </c>
+      <c r="J155" s="5">
         <v>20280523</v>
       </c>
-      <c r="K155" s="15">
+      <c r="K155" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4948,16 +4913,16 @@
       <c r="G156" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H156" s="7">
+      <c r="H156" s="5">
         <v>20280609</v>
       </c>
-      <c r="I156" s="15">
-        <v>500</v>
-      </c>
-      <c r="J156" s="8">
+      <c r="I156" s="9">
+        <v>500</v>
+      </c>
+      <c r="J156" s="5">
         <v>20280613</v>
       </c>
-      <c r="K156" s="15">
+      <c r="K156" s="9">
         <v>500</v>
       </c>
     </row>
@@ -4977,16 +4942,16 @@
       <c r="G157" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H157" s="7">
+      <c r="H157" s="5">
         <v>20280630</v>
       </c>
-      <c r="I157" s="15">
-        <v>500</v>
-      </c>
-      <c r="J157" s="8">
+      <c r="I157" s="9">
+        <v>500</v>
+      </c>
+      <c r="J157" s="5">
         <v>20280704</v>
       </c>
-      <c r="K157" s="15">
+      <c r="K157" s="9">
         <v>500</v>
       </c>
     </row>
@@ -5006,16 +4971,16 @@
       <c r="G158" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H158" s="7">
+      <c r="H158" s="5">
         <v>20280721</v>
       </c>
-      <c r="I158" s="15">
-        <v>500</v>
-      </c>
-      <c r="J158" s="8">
+      <c r="I158" s="9">
+        <v>500</v>
+      </c>
+      <c r="J158" s="5">
         <v>20280725</v>
       </c>
-      <c r="K158" s="15">
+      <c r="K158" s="9">
         <v>500</v>
       </c>
     </row>
@@ -5035,16 +5000,16 @@
       <c r="G161" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H161" s="7">
+      <c r="H161" s="5">
         <v>20280526</v>
       </c>
-      <c r="I161" s="15">
-        <v>500</v>
-      </c>
-      <c r="J161" s="8">
+      <c r="I161" s="9">
+        <v>500</v>
+      </c>
+      <c r="J161" s="5">
         <v>20280530</v>
       </c>
-      <c r="K161" s="15">
+      <c r="K161" s="9">
         <v>500</v>
       </c>
     </row>
@@ -5064,16 +5029,16 @@
       <c r="G162" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H162" s="7">
+      <c r="H162" s="5">
         <v>20280602</v>
       </c>
-      <c r="I162" s="15">
-        <v>500</v>
-      </c>
-      <c r="J162" s="8">
+      <c r="I162" s="9">
+        <v>500</v>
+      </c>
+      <c r="J162" s="5">
         <v>20280606</v>
       </c>
-      <c r="K162" s="15">
+      <c r="K162" s="9">
         <v>500</v>
       </c>
     </row>
@@ -5093,16 +5058,16 @@
       <c r="G163" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H163" s="7">
+      <c r="H163" s="5">
         <v>20280616</v>
       </c>
-      <c r="I163" s="15">
-        <v>500</v>
-      </c>
-      <c r="J163" s="8">
+      <c r="I163" s="9">
+        <v>500</v>
+      </c>
+      <c r="J163" s="5">
         <v>20280620</v>
       </c>
-      <c r="K163" s="15">
+      <c r="K163" s="9">
         <v>500</v>
       </c>
     </row>
@@ -5122,16 +5087,16 @@
       <c r="G164" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H164" s="7">
+      <c r="H164" s="5">
         <v>20280623</v>
       </c>
-      <c r="I164" s="15">
-        <v>500</v>
-      </c>
-      <c r="J164" s="8">
+      <c r="I164" s="9">
+        <v>500</v>
+      </c>
+      <c r="J164" s="5">
         <v>20280627</v>
       </c>
-      <c r="K164" s="15">
+      <c r="K164" s="9">
         <v>500</v>
       </c>
     </row>
@@ -5151,16 +5116,16 @@
       <c r="G165" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H165" s="7">
+      <c r="H165" s="5">
         <v>20280707</v>
       </c>
-      <c r="I165" s="15">
-        <v>500</v>
-      </c>
-      <c r="J165" s="8">
+      <c r="I165" s="9">
+        <v>500</v>
+      </c>
+      <c r="J165" s="5">
         <v>20280711</v>
       </c>
-      <c r="K165" s="15">
+      <c r="K165" s="9">
         <v>500</v>
       </c>
     </row>
@@ -5180,16 +5145,16 @@
       <c r="G166" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H166" s="7">
+      <c r="H166" s="5">
         <v>20280714</v>
       </c>
-      <c r="I166" s="15">
-        <v>500</v>
-      </c>
-      <c r="J166" s="8">
+      <c r="I166" s="9">
+        <v>500</v>
+      </c>
+      <c r="J166" s="5">
         <v>20280718</v>
       </c>
-      <c r="K166" s="15">
+      <c r="K166" s="9">
         <v>500</v>
       </c>
     </row>
